--- a/AutomatingMicrosoftExcel/StudentScores.xlsx
+++ b/AutomatingMicrosoftExcel/StudentScores.xlsx
@@ -319,6 +319,9 @@
       <c r="C2" s="1" t="n">
         <v>64</v>
       </c>
+      <c r="D2" s="0" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
@@ -330,6 +333,9 @@
       <c r="C3" s="1" t="n">
         <v>77</v>
       </c>
+      <c r="D3" s="0" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
@@ -341,6 +347,9 @@
       <c r="C4" s="1" t="n">
         <v>59</v>
       </c>
+      <c r="D4" s="0" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
@@ -352,6 +361,9 @@
       <c r="C5" s="1" t="n">
         <v>50</v>
       </c>
+      <c r="D5" s="0" t="n">
+        <v>16.5</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
@@ -363,6 +375,9 @@
       <c r="C6" s="1" t="n">
         <v>79</v>
       </c>
+      <c r="D6" s="0" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
@@ -374,6 +389,9 @@
       <c r="C7" s="1" t="n">
         <v>92</v>
       </c>
+      <c r="D7" s="0" t="n">
+        <v>27.261</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
@@ -385,6 +403,9 @@
       <c r="C8" s="1" t="n">
         <v>42</v>
       </c>
+      <c r="D8" s="0" t="n">
+        <v>12.18</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
@@ -396,6 +417,9 @@
       <c r="C9" s="1" t="n">
         <v>32</v>
       </c>
+      <c r="D9" s="0" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
@@ -407,6 +431,9 @@
       <c r="C10" s="1" t="n">
         <v>64</v>
       </c>
+      <c r="D10" s="0" t="n">
+        <v>17.1</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
@@ -418,6 +445,9 @@
       <c r="C11" s="1" t="n">
         <v>72</v>
       </c>
+      <c r="D11" s="0" t="n">
+        <v>20.7</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
@@ -429,6 +459,9 @@
       <c r="C12" s="1" t="n">
         <v>74.98</v>
       </c>
+      <c r="D12" s="0" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
@@ -440,6 +473,9 @@
       <c r="C13" s="1" t="n">
         <v>66</v>
       </c>
+      <c r="D13" s="0" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
@@ -451,6 +487,9 @@
       <c r="C14" s="1" t="n">
         <v>94</v>
       </c>
+      <c r="D14" s="0" t="n">
+        <v>27.3</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
@@ -461,6 +500,9 @@
       </c>
       <c r="C15" s="1" t="n">
         <v>87</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>25.5</v>
       </c>
     </row>
   </sheetData>

--- a/AutomatingMicrosoftExcel/StudentScores.xlsx
+++ b/AutomatingMicrosoftExcel/StudentScores.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t xml:space="preserve">Students</t>
   </si>
@@ -80,6 +80,9 @@
   </si>
   <si>
     <t xml:space="preserve">Ama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aq</t>
   </si>
 </sst>
 </file>
@@ -504,6 +507,9 @@
       <c r="D15" s="0" t="n">
         <v>25.5</v>
       </c>
+      <c r="F15" s="0" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
